--- a/mappings/subscriptions_mapping.xlsx
+++ b/mappings/subscriptions_mapping.xlsx
@@ -15,11 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Subscriptions → sale.order'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SubTypes → sub.plan'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SubLines → order.line'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ReasonCodes → close.reason'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Items → product.template'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Subscriptions → sale.order'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SubTypes → sub.plan'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SubLines → order.line'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ReasonCodes → close.reason'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Items → product.template'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,8 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,6 +541,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Related Model</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -575,7 +581,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Always preserve Exact primary key for reconciliation and re-run safety.</t>
         </is>
@@ -612,7 +619,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Exact's business-facing subscription number. Odoo auto-generates 'name' (Order Reference), so this goes to a custom field.</t>
         </is>
@@ -649,7 +657,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Subscription description. Odoo sale.order has no 'description' field — 'name' is the auto-generated order reference, 'note' is terms &amp; conditions, 'internal_note' is internal. Safest as custom.</t>
         </is>
@@ -678,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.partner</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -687,6 +696,11 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>res.partner</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Subscriber account. Requires lookup: Exact Account GUID → Odoo res.partner.</t>
         </is>
@@ -723,7 +737,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Contact person GUID on subscriber side. Odoo has no direct contact-person field on sale.order. Consider resolving to a child res.partner if contact data is migrated.</t>
         </is>
@@ -762,6 +777,11 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from OrderedByContactPerson relation.</t>
         </is>
       </c>
@@ -799,6 +819,11 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from OrderedBy → res.partner.name.</t>
         </is>
       </c>
@@ -826,7 +851,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.partner</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -835,6 +860,11 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>res.partner</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Invoice-to account. Requires same Account → res.partner lookup.</t>
         </is>
@@ -871,7 +901,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Contact person on invoice-to side. No native sale.order equivalent for contact-level granularity.</t>
         </is>
@@ -910,6 +941,11 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from InvoiceToContactPerson relation.</t>
         </is>
       </c>
@@ -947,6 +983,11 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from InvoiceTo → res.partner.name.</t>
         </is>
       </c>
@@ -982,7 +1023,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Exact DateTime → Odoo date (strip time component).</t>
         </is>
@@ -1019,7 +1061,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Odoo: 'If set in advance, the subscription will be set to renew 1 month before the date and will be closed on the date set in this field.'</t>
         </is>
@@ -1056,7 +1099,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>No native cancellation-date field in Odoo. Odoo tracks closure via subscription_state and close_reason_id but not the cancellation date itself.</t>
         </is>
@@ -1093,7 +1137,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Date invoicing begins. Odoo's next_invoice_date is the rolling next date, not the original start. Safest as custom.</t>
         </is>
@@ -1130,7 +1175,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Date up to which invoicing has been completed. Odoo has last_invoice_date (date of last invoice), which is close but semantically different — Exact means 'period covered', Odoo means 'date generated'. Custom avoids ambiguity.</t>
         </is>
@@ -1167,7 +1213,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Direct mapping.</t>
         </is>
@@ -1204,7 +1251,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Direct mapping.</t>
         </is>
@@ -1233,7 +1281,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>many2one → sale.subscription.plan</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1242,6 +1290,11 @@
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>sale.subscription.plan</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Map via SubscriptionTypes → sale.subscription.plan migration. Requires that SubscriptionTypes are migrated first.</t>
         </is>
@@ -1280,6 +1333,11 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from SubscriptionType → sale.subscription.plan.</t>
         </is>
       </c>
@@ -1317,6 +1375,11 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from SubscriptionType → sale.subscription.plan.name.</t>
         </is>
       </c>
@@ -1352,7 +1415,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Day-of-month (or weekday) for invoice generation. Odoo's sale.subscription.plan has billing_first_day (boolean: align to 1st), which is much simpler. No equivalent for arbitrary day selection.</t>
         </is>
@@ -1381,7 +1445,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.currency</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1390,6 +1454,11 @@
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>res.currency</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Exact stores currency as ISO code string. Resolve to res.currency record by name/code.</t>
         </is>
@@ -1426,7 +1495,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Both are customer-side purchase order references.</t>
         </is>
@@ -1455,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>many2one → account.payment.term</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1464,6 +1534,11 @@
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>account.payment.term</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Requires mapping Exact payment condition codes → Odoo payment terms.</t>
         </is>
@@ -1502,6 +1577,11 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from PaymentCondition → account.payment.term.name.</t>
         </is>
       </c>
@@ -1529,7 +1609,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>many2one → sale.order.close.reason</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1538,6 +1618,11 @@
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>sale.order.close.reason</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Map via SubscriptionReasonCodes → sale.order.close.reason migration (see ReasonCodes sheet).</t>
         </is>
@@ -1576,6 +1661,11 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from ReasonCancelled → sale.order.close.reason.</t>
         </is>
       </c>
@@ -1613,6 +1703,11 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from ReasonCancelled → sale.order.close.reason.name.</t>
         </is>
       </c>
@@ -1648,7 +1743,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Exact classification concept. No Odoo equivalent. Odoo has tag_ids (many2many → crm.tag) which could be used alternatively, but a custom field preserves the original GUID for traceability.</t>
         </is>
@@ -1687,6 +1783,11 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from Classification relation.</t>
         </is>
       </c>
@@ -1724,6 +1825,11 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from Classification relation.</t>
         </is>
       </c>
@@ -1751,7 +1857,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1760,6 +1866,11 @@
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Requires user mapping: Exact user GUID → Odoo res.users. May default to admin if user mapping is not in scope.</t>
         </is>
@@ -1798,6 +1909,11 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from Creator → res.users.name.</t>
         </is>
       </c>
@@ -1825,7 +1941,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1834,6 +1950,11 @@
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Same user mapping requirement as Creator.</t>
         </is>
@@ -1872,6 +1993,11 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from Modifier → res.users.name.</t>
         </is>
       </c>
@@ -1899,7 +2025,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.company</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1908,6 +2034,11 @@
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>res.company</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Exact Division ≈ Odoo Company. Requires division-to-company mapping.</t>
         </is>
@@ -1944,7 +2075,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Best fit for additional subscription info. Odoo 'internal_note' is internal-facing free text. Wrap plain text in &lt;p&gt; tags if needed.</t>
         </is>
@@ -1981,7 +2113,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Exact-specific: blocks time cost entry. No Odoo equivalent.</t>
         </is>
@@ -2018,7 +2151,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Exact-specific: indicates if subscription was printed. No Odoo equivalent.</t>
         </is>
@@ -2055,7 +2189,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Reference to Exact Project. Odoo sale.order does not have a native project link in the subscription context. If project module is installed, a custom many2one → project.project could be used instead.</t>
         </is>
@@ -2084,7 +2219,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>one2many → sale.order.line</t>
+          <t>one2many</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2093,6 +2228,11 @@
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>sale.order.line</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Structural: lines are migrated separately per the SubLines sheet.</t>
         </is>
@@ -2129,7 +2269,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Structural reference. No Odoo equivalent. Could become a separate custom model or JSON blob if needed.</t>
         </is>
@@ -2166,7 +2307,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Structural reference. No Odoo equivalent. Same approach as above.</t>
         </is>
@@ -2203,7 +2345,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Always set to True for migrated subscription records.</t>
         </is>
@@ -2240,7 +2383,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Derive from Exact lifecycle: if CancellationDate is set → '6_churn' or '5_renewed'; if EndDate &lt; today → '6_churn'; if StartDate ≤ today ≤ EndDate → '3_progress'; etc. Requires mapping logic.</t>
         </is>
@@ -2277,7 +2421,8 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Auto-generated by Odoo on creation (e.g. 'S00001'). Could optionally embed Exact Number via origin field or let Odoo sequence handle it.</t>
         </is>
@@ -2314,14 +2459,15 @@
           <t>sale.order</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Odoo sales order state (draft/sale/cancel). Migrated subscriptions should typically be set to 'sale'.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2332,7 +2478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2341,7 +2487,8 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2377,6 +2524,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Related Model</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -2412,7 +2564,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Always preserve Exact primary key.</t>
         </is>
@@ -2449,7 +2602,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Exact type code. Odoo plan has 'name' but no separate code field. Useful for reference/lookups.</t>
         </is>
@@ -2486,7 +2640,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Odoo plan name.</t>
         </is>
@@ -2515,7 +2670,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.company</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2524,6 +2679,11 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>res.company</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Division → Company mapping.</t>
         </is>
@@ -2560,7 +2720,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2585,7 +2746,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2593,7 +2754,12 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2628,6 +2794,11 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from Creator → res.users.name.</t>
         </is>
       </c>
@@ -2663,7 +2834,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2688,7 +2860,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2696,7 +2868,12 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2731,6 +2908,11 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from Modifier → res.users.name.</t>
         </is>
       </c>
@@ -2766,7 +2948,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Invoice period numeric value → Odoo billing period value.</t>
         </is>
@@ -2803,7 +2986,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Requires value conversion: Exact wk→week, mm→month, qt→(3 months), hy→(6 months), yy→year. Quarter and half-year need decomposition (e.g., qt → 3 month, hy → 6 month).</t>
         </is>
@@ -2840,7 +3024,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Notice period for cancellation. Odoo auto_close_limit is about unpaid-invoice auto-closure (different concept).</t>
         </is>
@@ -2877,7 +3062,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Unit of cancellation notice period.</t>
         </is>
@@ -2914,7 +3100,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>No direct Odoo equivalent. Odoo handles renewal via user_extend (boolean) and the renewal workflow.</t>
         </is>
@@ -2951,7 +3138,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2984,7 +3172,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3017,7 +3206,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3050,7 +3240,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1=Use item prices, 2=Use current subscription prices. No Odoo equivalent.</t>
         </is>
@@ -3087,7 +3278,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Total subscription contract period. Distinct from billing period.</t>
         </is>
@@ -3124,7 +3316,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3157,7 +3350,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>0=No, 1=Manual, 2=Automatic. Odoo has user_extend (boolean) which is a loose analog.</t>
         </is>
@@ -3194,7 +3388,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Days before/after period to generate invoice. No Odoo plan equivalent.</t>
         </is>
@@ -3231,7 +3426,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>1=Never, 2=Before period, 3=After period.</t>
         </is>
@@ -3268,7 +3464,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3301,7 +3498,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3334,7 +3532,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>1=Never, 2=When available.</t>
         </is>
@@ -3371,7 +3570,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1=Based on account, 2=Email, 3=Documents, 4=Digital postbox, 5=Send and track, 6=Peppol.</t>
         </is>
@@ -3408,7 +3608,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>1=Company email, 2=Main user email.</t>
         </is>
@@ -3445,7 +3646,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3478,7 +3680,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>1=Ratio based, 2=Zero Invoice, 3=Never invoiced.</t>
         </is>
@@ -3515,7 +3718,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>0=Never, 1=Always, 2=Based on account.</t>
         </is>
@@ -3552,7 +3756,8 @@
           <t>sale.subscription.plan</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Additional notes. No notes field on Odoo plan.</t>
         </is>
@@ -3591,12 +3796,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>Exact Premium-only custom field endpoint. Not a data field — skip.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3607,7 +3817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3616,7 +3826,8 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3652,6 +3863,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Related Model</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -3687,7 +3903,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Always preserve Exact primary key.</t>
         </is>
@@ -3716,7 +3933,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>many2one → sale.order</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -3725,6 +3942,11 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>sale.order</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Link to parent subscription → sale.order. Resolve via x_aa_exact_id on sale.order.</t>
         </is>
@@ -3761,7 +3983,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Line ordering. Odoo uses 'sequence' for display order.</t>
         </is>
@@ -3798,7 +4021,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Line description → Odoo 'name' (Description field on order line).</t>
         </is>
@@ -3827,7 +4051,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>many2one → product.product</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3836,6 +4060,11 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>product.product</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Exact Item → Odoo product. Resolve: Item GUID → product.template (via x_aa_exact_id) → product_variant_id → product.product. See Items sheet.</t>
         </is>
@@ -3874,6 +4103,11 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from Item → product.product.name.</t>
         </is>
       </c>
@@ -3909,7 +4143,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Direct mapping.</t>
         </is>
@@ -3946,7 +4181,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Unit price → Odoo price_unit. Note: Exact says 'price * unit factor' — verify whether this is the raw price or already factored.</t>
         </is>
@@ -3983,7 +4219,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Net price in transaction currency. Odoo computes price_subtotal. Store for reconciliation.</t>
         </is>
@@ -4020,7 +4257,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Discount percentage. Direct mapping. Verify Exact uses percentage (0-100) same as Odoo.</t>
         </is>
@@ -4057,7 +4295,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Amount in default (company) currency. Useful for reconciliation.</t>
         </is>
@@ -4094,7 +4333,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Amount in foreign (transaction) currency. Store for reconciliation.</t>
         </is>
@@ -4131,7 +4371,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Line-level start date. Odoo subscription lines do not have per-line start/end dates.</t>
         </is>
@@ -4168,7 +4409,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Line-level end date.</t>
         </is>
@@ -4205,7 +4447,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Exact line type integer code. No clean Odoo equivalent. Stored as-is; description denormalized alongside.</t>
         </is>
@@ -4242,7 +4485,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Denormalized from SubscriptionLineTypes table. Stored alongside x_aa_line_type so the code is human-readable.</t>
         </is>
@@ -4279,7 +4523,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Exact cost center. Odoo uses analytic accounts (different paradigm). Custom for safety.</t>
         </is>
@@ -4316,7 +4561,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Exact cost unit. Same rationale as Costcenter.</t>
         </is>
@@ -4345,7 +4591,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>many2one → uom.uom</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4354,6 +4600,11 @@
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>uom.uom</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Unit of measure code → Odoo UoM. Requires code → uom.uom lookup.</t>
         </is>
@@ -4392,6 +4643,11 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from UnitCode → uom.uom.name.</t>
         </is>
       </c>
@@ -4419,7 +4675,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>many2many → account.tax</t>
+          <t>many2many</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4428,6 +4684,11 @@
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>account.tax</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>VAT code → Odoo tax. Requires tax code mapping from Exact → Odoo account.tax.</t>
         </is>
@@ -4466,6 +4727,11 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from VATCode → account.tax.name.</t>
         </is>
       </c>
@@ -4501,7 +4767,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>VAT amount in transaction currency. Odoo computes tax amounts. Store for reconciliation.</t>
         </is>
@@ -4530,7 +4797,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.company</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -4539,6 +4806,11 @@
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>res.company</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Division → Company mapping.</t>
         </is>
@@ -4577,6 +4849,11 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>Redundant with parent subscription number. Derivable from order_id → sale.order.x_aa_subscription_number.</t>
         </is>
       </c>
@@ -4612,7 +4889,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4645,7 +4923,8 @@
           <t>sale.order.line</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Additional line notes. Odoo has no per-line notes field separate from 'name'.</t>
         </is>
@@ -4684,6 +4963,11 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>Exact Premium-only custom field endpoint. Not a data field — skip.</t>
         </is>
       </c>
@@ -4711,7 +4995,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>many2one → product.template</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4721,12 +5005,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>product.template</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>Auto-resolved by Odoo from product_id. No migration action needed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4737,7 +5026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4746,7 +5035,8 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4782,6 +5072,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Related Model</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -4817,7 +5112,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Always preserve Exact primary key.</t>
         </is>
@@ -4854,7 +5150,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Exact reason code. Odoo close reason has no code field.</t>
         </is>
@@ -4891,7 +5188,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Description → Odoo 'Reason' field.</t>
         </is>
@@ -4928,7 +5226,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Exact active flag. Odoo close reason has no 'active' field (no archive toggle).</t>
         </is>
@@ -4965,7 +5264,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Odoo has retention_message (html) which is customer-facing portal copy, not internal notes. Different purpose.</t>
         </is>
@@ -5002,7 +5302,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Odoo close reasons appear to be global/cross-company. Stored as custom for traceability.</t>
         </is>
@@ -5039,7 +5340,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5064,7 +5366,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -5072,7 +5374,12 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5107,6 +5414,11 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -5142,7 +5454,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5167,7 +5480,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -5175,7 +5488,12 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5210,6 +5528,11 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -5247,6 +5570,11 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>Exact Premium-only custom field endpoint — skip.</t>
         </is>
       </c>
@@ -5282,7 +5610,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Odoo ordering field. Default to 10 or assign sequentially.</t>
         </is>
@@ -5319,7 +5648,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Default to True or False based on business preference.</t>
         </is>
@@ -5356,7 +5686,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Set to False for all migrated records.</t>
         </is>
@@ -5393,7 +5724,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Customer-facing retention copy. No Exact equivalent. Leave empty.</t>
         </is>
@@ -5430,7 +5762,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Leave empty.</t>
         </is>
@@ -5467,7 +5800,8 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Leave empty.</t>
         </is>
@@ -5504,14 +5838,15 @@
           <t>sale.order.close.reason</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Set to True if retention_message is left empty.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5522,7 +5857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5531,7 +5866,8 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5567,6 +5903,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Related Model</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -5602,7 +5943,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Always preserve Exact primary key. Critical for resolving SubscriptionLines.Item → product.product (via template's product_variant_id).</t>
         </is>
@@ -5639,7 +5981,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Exact item code → Odoo Internal Reference. Both serve as the business-facing product code.</t>
         </is>
@@ -5676,7 +6019,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Exact search code. Odoo has no separate search code field (search is full-text on name/default_code/barcode).</t>
         </is>
@@ -5713,7 +6057,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Direct mapping.</t>
         </is>
@@ -5750,7 +6095,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Exact item description → Odoo product name. Note: Exact Description is max 60 chars, Odoo name is unlimited.</t>
         </is>
@@ -5787,7 +6133,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Longer description (255 chars). Maps well to Odoo 'Sales Description' which is copied to SO lines, delivery orders, and invoices.</t>
         </is>
@@ -5824,7 +6171,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Additional notes → Odoo general description (html). Wrap plain text in &lt;p&gt; tags.</t>
         </is>
@@ -5861,7 +6209,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Standard sales price → Odoo Sales Price.</t>
         </is>
@@ -5898,7 +6247,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Standard cost → Odoo Cost field. Used for margin calculations and inventory valuation.</t>
         </is>
@@ -5935,7 +6285,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Exact's running average cost. Odoo computes AVCO internally via stock valuation layers — not a writable field in the same way. Preserve for reconciliation.</t>
         </is>
@@ -5972,7 +6323,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Proposed new cost price. No Odoo equivalent (Odoo updates cost directly or via valuation).</t>
         </is>
@@ -6001,7 +6353,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.currency</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -6010,6 +6362,11 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>res.currency</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Currency of cost prices. Resolve ISO code → res.currency.</t>
         </is>
@@ -6038,7 +6395,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>many2one → product.category</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -6047,6 +6404,11 @@
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>product.category</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Exact ItemGroup → Odoo product category. ItemGroups are not being migrated as a separate domain; defer resolution and default all products to Odoo's built-in 'All' category (id=1).</t>
         </is>
@@ -6085,6 +6447,11 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field. Value derivable from ItemGroup → product.category.name.</t>
         </is>
       </c>
@@ -6122,6 +6489,11 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -6149,7 +6521,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>many2one → uom.uom</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6158,6 +6530,11 @@
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>uom.uom</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Default unit of measure. Resolve Exact unit code → Odoo uom.uom. Also sets uom_po_id if purchase UoM should match.</t>
         </is>
@@ -6196,6 +6573,11 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -6231,7 +6613,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>A=Area, L=Length, O=Other, T=Time, V=Volume, W=Weight. Odoo infers UoM category from the uom.uom record itself. Stored for reference.</t>
         </is>
@@ -6260,7 +6643,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>many2many → account.tax</t>
+          <t>many2many</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -6269,6 +6652,11 @@
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>account.tax</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Default sales tax. Resolve Exact VAT code → Odoo account.tax.</t>
         </is>
@@ -6307,6 +6695,11 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -6342,7 +6735,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Exact taxability flag. In Odoo, taxability is determined by which taxes_id records are assigned. Stored for reference.</t>
         </is>
@@ -6379,7 +6773,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. 'Can be sold' flag.</t>
         </is>
@@ -6416,7 +6811,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. 'Can be purchased' flag.</t>
         </is>
@@ -6453,7 +6849,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Exact stock item ≈ Odoo 'Track Inventory'. Note: subscription items are often services (is_storable=False), so verify per item.</t>
         </is>
@@ -6490,7 +6887,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Odoo has 'weight' (net weight for shipping). Gross weight has no native field.</t>
         </is>
@@ -6527,7 +6925,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Net weight → Odoo weight (used in shipping calculations).</t>
         </is>
@@ -6564,7 +6963,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Odoo uses weight_uom_name derived from system UoM settings, not a per-product weight unit. Stored for reference.</t>
         </is>
@@ -6603,6 +7003,11 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>Current stock quantity. Odoo computes qty_available from stock.quant — not a writable product field. Stock migration is a separate workstream.</t>
         </is>
       </c>
@@ -6638,7 +7043,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Statistical/commodity code → Odoo HS Code. Both are used for international trade declarations.</t>
         </is>
@@ -6675,7 +7081,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Statistical net weight for trade reporting. No separate Odoo field.</t>
         </is>
@@ -6712,7 +7119,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6745,7 +7153,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6770,7 +7179,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>many2one → account.account</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6779,6 +7188,11 @@
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Revenue GL account → Odoo Income Account. Resolve Exact GL GUID → Odoo account.account. Falls back to product category setting if empty.</t>
         </is>
@@ -6817,6 +7231,11 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -6854,6 +7273,11 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -6881,7 +7305,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>many2one → account.account</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -6890,6 +7314,11 @@
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>account.account</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Cost GL account → Odoo Expense Account. Same resolution as GLRevenue.</t>
         </is>
@@ -6928,6 +7357,11 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -6965,6 +7399,11 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -7000,7 +7439,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Stock valuation GL account. In Odoo this is typically set at the product.category level (property_stock_valuation_account_id), not per product. Stored as custom.</t>
         </is>
@@ -7039,6 +7479,11 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -7076,6 +7521,11 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -7111,7 +7561,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>WIP revenue account. No per-product Odoo equivalent (Odoo WIP accounts are on product.category for manufacturing).</t>
         </is>
@@ -7150,6 +7601,11 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -7187,6 +7643,11 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -7222,7 +7683,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>WIP cost account. Same rationale as GLRevenueWorkInProgress.</t>
         </is>
@@ -7261,6 +7723,11 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -7298,6 +7765,11 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -7333,7 +7805,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Item validity start. In Odoo, product lifecycle is controlled by 'active' boolean, not date range. Store for reference; use to derive 'active' flag.</t>
         </is>
@@ -7370,7 +7843,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Item validity end. Same rationale as StartDate.</t>
         </is>
@@ -7399,7 +7873,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.company</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -7408,6 +7882,11 @@
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>res.company</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Division → Company mapping.</t>
         </is>
@@ -7444,7 +7923,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -7469,7 +7949,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -7477,7 +7957,12 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -7512,6 +7997,11 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -7547,7 +8037,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -7572,7 +8063,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>many2one → res.users</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7580,7 +8071,12 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>res.users</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -7615,6 +8111,11 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
           <t>Denormalized display field.</t>
         </is>
       </c>
@@ -7650,7 +8151,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Exact access control level. No Odoo equivalent.</t>
         </is>
@@ -7687,7 +8189,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Product image. Note: Exact's Picture field is write-only; actual image must be downloaded from PictureUrl. Odoo expects base64-encoded image in image_1920.</t>
         </is>
@@ -7724,7 +8227,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Original filename. No Odoo equivalent (Odoo stores images as blobs without filenames).</t>
         </is>
@@ -7763,6 +8267,11 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
           <t>Runtime URL, not migratable.</t>
         </is>
       </c>
@@ -7800,6 +8309,11 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
           <t>Runtime URL. Use during migration to download image for image_1920, but don't store the URL itself.</t>
         </is>
       </c>
@@ -7835,7 +8349,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Produced to inventory, not purchased. Odoo handles this via route_ids (Buy vs Manufacture). Custom for traceability.</t>
         </is>
@@ -7872,7 +8387,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Odoo has 'tracking' selection (none/lot/serial). Could derive tracking='serial' from this, but safer as custom + derive.</t>
         </is>
@@ -7909,7 +8425,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Batch tracking. Could derive tracking='lot'. Custom for traceability.</t>
         </is>
@@ -7948,6 +8465,11 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
           <t>Obsolete field per Exact docs. Use IsSerialItem instead.</t>
         </is>
       </c>
@@ -7985,6 +8507,11 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
           <t>Obsolete field per Exact docs. Use IsBatchItem instead.</t>
         </is>
       </c>
@@ -8020,7 +8547,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Whether fractional quantities are allowed. Odoo handles this via UoM rounding. Custom for reference.</t>
         </is>
@@ -8057,7 +8585,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Odoo has service_to_purchase for subcontract services and a separate subcontracting module. Custom for traceability.</t>
         </is>
@@ -8094,7 +8623,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>No Odoo equivalent.</t>
         </is>
@@ -8131,7 +8661,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Time/labor item. In Odoo this would typically be type='service' + service_type='timesheet'. Custom for traceability.</t>
         </is>
@@ -8168,7 +8699,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Odoo uses is_published (boolean) + website_id for eCommerce visibility. Different mechanism, custom for reference.</t>
         </is>
@@ -8205,7 +8737,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Exact hosting/package concept. No Odoo equivalent.</t>
         </is>
@@ -8242,7 +8775,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Package/contract type flag. No Odoo equivalent.</t>
         </is>
@@ -8279,7 +8813,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Voucher functionality flag. No Odoo equivalent.</t>
         </is>
@@ -8316,7 +8851,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Default batch quantity. No direct Odoo equivalent.</t>
         </is>
@@ -8353,7 +8889,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Assembly lead time. Odoo has sale_delay (Customer Lead Time) for delivery promises, and produce_delay on MRP. Different semantics — custom.</t>
         </is>
@@ -8390,7 +8927,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Copy sales remarks to lines. No Odoo equivalent.</t>
         </is>
@@ -8427,7 +8965,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Assemble at delivery. No direct Odoo equivalent.</t>
         </is>
@@ -8464,7 +9003,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Exact ItemClass code (ClassID 1). Exact supports up to 10 classification dimensions per item. Odoo has no equivalent multi-axis classification. All 10 stored as custom.</t>
         </is>
@@ -8501,7 +9041,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>ItemClass ClassID 2.</t>
         </is>
@@ -8538,7 +9079,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>ItemClass ClassID 3.</t>
         </is>
@@ -8575,7 +9117,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>ItemClass ClassID 4.</t>
         </is>
@@ -8612,7 +9155,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>ItemClass ClassID 5.</t>
         </is>
@@ -8649,7 +9193,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>ItemClass ClassID 6.</t>
         </is>
@@ -8686,7 +9231,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>ItemClass ClassID 7.</t>
         </is>
@@ -8723,7 +9269,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>ItemClass ClassID 8.</t>
         </is>
@@ -8760,7 +9307,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>ItemClass ClassID 9.</t>
         </is>
@@ -8797,7 +9345,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>ItemClass ClassID 10.</t>
         </is>
@@ -8834,7 +9383,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Exact generic custom boolean fields (01-05). Meaning is customer-specific. All stored as x_aa_ custom fields.</t>
         </is>
@@ -8871,7 +9421,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G91" s="2" t="n"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -8904,7 +9455,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G92" s="2" t="n"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -8937,7 +9489,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G93" s="2" t="n"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -8970,7 +9523,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G94" s="2" t="n"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -9003,7 +9557,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Exact generic custom date fields (01-05). Meaning is customer-specific.</t>
         </is>
@@ -9040,7 +9595,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G96" s="2" t="n"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -9073,7 +9629,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G97" s="2" t="n"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -9106,7 +9663,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G98" s="2" t="n"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -9139,7 +9697,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G99" s="2" t="n"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -9172,7 +9731,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Exact generic custom numeric fields (01-08). Meaning is customer-specific.</t>
         </is>
@@ -9209,7 +9769,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G101" s="2" t="n"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -9242,7 +9803,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G102" s="2" t="n"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -9275,7 +9837,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G103" s="2" t="n"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -9308,7 +9871,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G104" s="2" t="n"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -9341,7 +9905,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G105" s="2" t="n"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -9374,7 +9939,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G106" s="2" t="n"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -9407,7 +9973,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G107" s="2" t="n"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -9440,7 +10007,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Exact generic custom text fields (01-10). Meaning is customer-specific.</t>
         </is>
@@ -9477,7 +10045,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G109" s="2" t="n"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -9510,7 +10079,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G110" s="2" t="n"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -9543,7 +10113,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G111" s="2" t="n"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -9576,7 +10147,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G112" s="2" t="n"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -9609,7 +10181,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G113" s="2" t="n"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -9642,7 +10215,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G114" s="2" t="n"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -9675,7 +10249,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G115" s="2" t="n"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -9708,7 +10283,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G116" s="2" t="n"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -9741,7 +10317,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G117" s="2" t="n"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -9776,6 +10353,11 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
           <t>Exact Premium-only custom field endpoint — skip.</t>
         </is>
       </c>
@@ -9811,7 +10393,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>CRITICAL for subscriptions. Set to True for all items that appear on SubscriptionLines. This flag makes Odoo treat the product as a subscription product.</t>
         </is>
@@ -9848,7 +10431,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Odoo product type. Subscription items are typically 'service'. For physical subscription products (boxes, etc.), use 'consu' or 'product'. Derive from Exact IsStockItem / IsTime / item characteristics.</t>
         </is>
@@ -9885,7 +10469,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Should be 'order' (Ordered quantities) for subscription products per Odoo docs. 'delivery' causes issues with recurring invoice creation.</t>
         </is>
@@ -9922,7 +10507,8 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Derive from Exact StartDate/EndDate: if EndDate is set and &lt; today → False; otherwise True.</t>
         </is>
@@ -9959,14 +10545,15 @@
           <t>product.template</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Normally derived from IsSalesItem (Direct mapping above). Listed here as reminder: must be True for subscription products to appear on SO lines.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
